--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -506,7 +506,6 @@
           <t>t1_intro</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>t1_timeout</t>
@@ -630,7 +629,6 @@
           <t>ep_test1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>노드 0 (도입, 선택지 없음 → 계속)</t>
@@ -668,8 +666,6 @@
           <t>노드 A (조건부 선택지 테스트)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -682,14 +678,11 @@
           <t>ep_test1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>노드 B (탐색·인벤토리 테스트)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -734,14 +727,11 @@
           <t>ep_test1</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>노드 D (결말·스탯 테스트)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -754,7 +744,6 @@
           <t>ep_test1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>시간 초과 노드</t>
@@ -765,7 +754,6 @@
           <t>END:end_t1_timeout</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -788,8 +776,6 @@
           <t>노드 A (에피소드 2)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -802,7 +788,6 @@
           <t>ep_test2</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>시간 초과 노드 (에피소드 2)</t>
@@ -813,7 +798,6 @@
           <t>END:end_t2_timeout</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -897,10 +881,6 @@
           <t>선택지 1 (일반)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>t1_b</t>
@@ -933,8 +913,6 @@
           <t>gray</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>t1_c</t>
@@ -967,8 +945,6 @@
           <t>hide</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>t1_c</t>
@@ -991,8 +967,6 @@
           <t>선택지 4 (대가형)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>체력 -10, 시간 -10</t>
@@ -1025,8 +999,6 @@
           <t>탐색 (spot_b)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>시간 -10</t>
@@ -1059,8 +1031,6 @@
           <t>빈 곳 탐색 (spot_empty)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>시간 -5</t>
@@ -1093,9 +1063,6 @@
           <t>잡동사니 9개 줍기 (인벤토리 초과)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>item:+junk*9</t>
@@ -1123,10 +1090,6 @@
           <t>노드 A로</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>t1_a</t>
@@ -1149,10 +1112,6 @@
           <t>정상 클리어</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>END:end_t1_clear</t>
@@ -1185,8 +1144,6 @@
           <t>gray</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>END:end_t1_good</t>
@@ -1219,7 +1176,6 @@
           <t>hide</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>item:+pill</t>
@@ -1289,8 +1245,6 @@
           <t>사망 테스트</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>체력 -999</t>
@@ -1323,8 +1277,6 @@
           <t>광기 테스트</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>정신력 -999</t>
@@ -1357,8 +1309,6 @@
           <t>시간 초과 테스트</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>시간 -999</t>
@@ -1391,10 +1341,6 @@
           <t>클리어</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>END:end_t2_clear</t>
@@ -1417,8 +1363,6 @@
           <t>시간 초과 테스트</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>시간 -999</t>
@@ -1540,7 +1484,6 @@
           <t>아이템 설명 2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>1</v>
       </c>
@@ -1566,7 +1509,6 @@
           <t>아이템 설명 3</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>1</v>
       </c>
@@ -1744,12 +1686,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="11.6" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1768,6 +1711,11 @@
           <t>traits</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>name_color</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1785,6 +1733,11 @@
           <t>tester</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>#D81B4A</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1797,7 +1750,6 @@
           <t>주인공 2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1810,7 +1762,11 @@
           <t>NPC 1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>#F2C200</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1893,7 +1849,6 @@
           <t>ep_test1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1906,7 +1861,6 @@
           <t>ep_test1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1919,7 +1873,6 @@
           <t>ep_test1</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1949,7 +1902,6 @@
           <t>ep_test2</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1962,7 +1914,6 @@
           <t>ep_test2</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1975,7 +1926,6 @@
           <t>ep_test2</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2129,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -2142,9 +2092,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2180,9 +2128,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -2225,9 +2171,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -2267,6 +2211,13 @@
       <c r="A21" t="inlineStr">
         <is>
           <t>표에 없는 열(메모 등)을 추가해도 변환 시 무시된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Characters.name_color: 대화 이름표 색 (#RRGGBB). 비우면 기본색.</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>t2_a</t>
+          <t>t2_npc1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -798,6 +798,62 @@
           <t>END:end_t2_timeout</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>t2_npc1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ep_test2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>char_npc</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>노드 N1 (NPC 1 대사)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>t2_npc2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>t2_npc2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ep_test2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>char_npc2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>노드 N2 (NPC 2 대사)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>t2_a</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1686,7 +1742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.8" customWidth="1" min="1" max="1"/>
@@ -1765,6 +1821,24 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>#F2C200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>char_npc2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NPC 2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>#4FC3F7</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2166,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2128,7 +2201,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -2171,7 +2243,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -14,8 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loot" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Characters" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endings" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abilities" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,13 +570,215 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="90" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>문법 요약 (이 시트는 변환 시 무시됨: 이름이 _로 시작)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>[조건] &amp; = AND, | = OR, ! = NOT, 괄호 () 사용 가능. 우선순위: ! &gt; &amp; &gt; |</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>has:knife  /  has:bandage&gt;=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>flag:door_open (에피소드 플래그)  /  wflag:ep1_clear (월드 플래그)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>stat:sanity&gt;=30   (비교: &gt; &gt;= &lt; &lt;= ==, 스탯: hp sanity time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>trait:medic (현재 주인공 능력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>[효과] ; 로 구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>item:+bandage  /  item:-bandage  /  item:+bandage*2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>stat:hp-10  /  stat:hp+10  /  stat:hp=50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>setflag:x  /  clearflag:x  /  setwflag:x</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>loot:spot_id (Loot 시트 확률 굴림, chance는 0~100 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>goto:node_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>[진행] 선택지 없는 노드는 next_node로 진행. END:&lt;ending_id&gt; 는 엔딩.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>show_mode: hide(조건 미충족 시 숨김) / gray(회색, 기본값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cost 는 표시용. 실제 차감은 effects 에 적는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>아이템 사용 시 소모도 use_effects 에 명시 (예: item:-bandage;stat:hp+20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Traits / world_flags_set 은 쉼표(,)로 여러 개.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>표에 없는 열(메모 등)을 추가해도 변환 시 무시된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Characters.name_color: 대화 이름표 색 (#RRGGBB). 비우면 기본색.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>[주사위 판정] d20 + 보정치 &gt;= dc 이면 성공. 성공 확률 = (21 - (dc - 보정치)) / 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>보정치 = 능력치(Characters.abilities + abil: 효과로 성장) + 소지 아이템 dice_bonus + 선택지 mod</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Choices.type: normal(기본) / item(condition 에 has: 필요, 가지고 있으면 반드시 성공) / dice</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>dice 선택지: check(능력치) dc(목표값) mod(상황 보정), 성공 → effects·next_node, 실패 → fail_effects·fail_next</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Abilities 시트: ability_id, name.  Characters.abilities: 'stat_a=3, stat_b=1'</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Items.dice_bonus: 'stat_a+2' 또는 'all+1' (소지 중이면 적용, 개수와 무관하게 1번)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>조건 abil:stat_a&gt;=3 / 효과 abil:stat_a+1 (육성)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -825,7 +1028,6 @@
           <t>t2_npc2</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -853,7 +1055,74 @@
           <t>t2_a</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>t1_e</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ep_test1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>노드 E (주사위 판정 테스트)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>t1_dice_ok</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ep_test1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>판정 성공 노드</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>t1_e</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>t1_dice_fail</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ep_test1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>판정 실패 노드</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>t1_e</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -866,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.4" customWidth="1" min="1" max="1"/>
@@ -877,6 +1146,12 @@
     <col width="24.4" customWidth="1" min="6" max="6"/>
     <col width="38.8" customWidth="1" min="7" max="7"/>
     <col width="27.6" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -920,6 +1195,36 @@
           <t>next_node</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dc</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>mod</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fail_effects</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>fail_next</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -974,6 +1279,11 @@
           <t>t1_c</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1006,6 +1316,11 @@
           <t>t1_c</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1432,6 +1747,222 @@
       <c r="H18" t="inlineStr">
         <is>
           <t>t2_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>c_d8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t1_d</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>판정 테스트로</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>t1_e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>c_e1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t1_e</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>판정 A (능력치 A, 목표 12)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>setflag:dice_ok</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>t1_dice_ok</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>dice</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stat_a</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>12</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>stat:hp-5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>t1_dice_fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>c_e2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t1_e</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>판정 B (능력치 B, 목표 10, 상황 보정 -5)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>t1_dice_ok</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>dice</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stat_b</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>t1_dice_fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>c_e3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t1_e</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>능력치 A 성장 (+1)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>abil:stat_a+1</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>t1_e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>c_e4</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t1_e</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>능력치 조건 (abil:stat_a&gt;=4)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>abil:stat_a&gt;=4</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>gray</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>t1_e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>c_e5</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t1_e</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>노드 D로</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>t1_d</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.2" customWidth="1" min="1" max="1"/>
@@ -1455,6 +1986,7 @@
     <col width="19.6" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="16.4" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1488,6 +2020,11 @@
           <t>stack_max</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dice_bonus</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1542,6 +2079,11 @@
       </c>
       <c r="F3" t="n">
         <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>stat_a+1</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1742,13 +2284,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="11.6" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1772,6 +2315,11 @@
           <t>name_color</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>abilities</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1794,6 +2342,11 @@
           <t>#D81B4A</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>stat_a=3, stat_b=0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1806,6 +2359,11 @@
           <t>주인공 2</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>stat_a=1, stat_b=2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1835,7 +2393,6 @@
           <t>NPC 2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>#4FC3F7</t>
@@ -2012,133 +2569,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="19.6" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>ability_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
+          <t>name</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>inventory_slots</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>인벤토리 칸 수</t>
+          <t>stat_a</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>능력치 A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hp_start</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>에피소드 시작 체력</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>hp_max</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>체력 최대치</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sanity_start</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>100</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>에피소드 시작 정신력</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>sanity_max</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>100</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>정신력 최대치</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>time_start</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>120</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>에피소드 시작 시간</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>time_max</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>120</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>시간 최대치</t>
+          <t>stat_b</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>능력치 B</t>
         </is>
       </c>
     </row>
@@ -2153,142 +2623,133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="19.6" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>문법 요약 (이 시트는 변환 시 무시됨: 이름이 _로 시작)</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>inventory_slots</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>인벤토리 칸 수</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[조건] &amp; = AND, | = OR, ! = NOT, 괄호 () 사용 가능. 우선순위: ! &gt; &amp; &gt; |</t>
+          <t>hp_start</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>에피소드 시작 체력</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>has:knife  /  has:bandage&gt;=2</t>
+          <t>hp_max</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>체력 최대치</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>flag:door_open (에피소드 플래그)  /  wflag:ep1_clear (월드 플래그)</t>
+          <t>sanity_start</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>에피소드 시작 정신력</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>stat:sanity&gt;=30   (비교: &gt; &gt;= &lt; &lt;= ==, 스탯: hp sanity time)</t>
+          <t>sanity_max</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>정신력 최대치</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>trait:medic (현재 주인공 능력)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>[효과] ; 로 구분</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>item:+bandage  /  item:-bandage  /  item:+bandage*2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>stat:hp-10  /  stat:hp+10  /  stat:hp=50</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>setflag:x  /  clearflag:x  /  setwflag:x</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>loot:spot_id (Loot 시트 확률 굴림, chance는 0~100 %)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>goto:node_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>[진행] 선택지 없는 노드는 next_node로 진행. END:&lt;ending_id&gt; 는 엔딩.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>show_mode: hide(조건 미충족 시 숨김) / gray(회색, 기본값)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cost 는 표시용. 실제 차감은 effects 에 적는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>아이템 사용 시 소모도 use_effects 에 명시 (예: item:-bandage;stat:hp+20).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Traits / world_flags_set 은 쉼표(,)로 여러 개.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>표에 없는 열(메모 등)을 추가해도 변환 시 무시된다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Characters.name_color: 대화 이름표 색 (#RRGGBB). 비우면 기본색.</t>
+          <t>time_start</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>120</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>에피소드 시작 시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>time_max</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>120</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>시간 최대치</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -16,7 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endings" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abilities" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlayerParts" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyParts" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyAttacks" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,7 +580,625 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>part_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>vital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>머리</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>torso</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>몸통</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>left_arm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>왼팔</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>right_arm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>오른팔</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>left_leg</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>왼다리</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>right_leg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>오른다리</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>enemy_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>enemy_test</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>적 A (테스트)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>enemy_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>part_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>hit_chance</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>vital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>enemy_test</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>머리</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>enemy_test</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>torso</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>몸통</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>enemy_test</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>left_arm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>왼팔</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>70</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>enemy_test</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>right_arm</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>오른팔</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>70</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>attack_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>enemy_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>part</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>targets</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>windup</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>atk_normal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>enemy_test</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>일반 공격 (테스트)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>right_arm</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>torso</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>atk_quick</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>enemy_test</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>속공 (테스트)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>left_arm</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>quick</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>left_arm</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>atk_combo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>enemy_test</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>연속 공격 (테스트)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>right_arm</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>head, right_leg</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>atk_feint</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>enemy_test</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>기만 공격 (테스트)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>feint</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>torso&gt;head</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -715,9 +1337,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -764,6 +1384,51 @@
       <c r="A30" t="inlineStr">
         <is>
           <t>조건 abil:stat_a&gt;=3 / 효과 abil:stat_a+1 (육성)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>[전투] PlayerParts: 플레이어 부위 (key = 회피 키 W/A/S/D, vital=Y 면 파괴 시 사망)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Enemies / EnemyParts(적별 부위, hit_chance %) / EnemyAttacks(적 공격)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EnemyAttacks.pattern: normal / quick / combo(targets 'head, torso' 순서대로) / feint(targets '전조&gt;실제')</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>EnemyAttacks.part: 이 공격을 쓰는 적 부위. 그 부위가 파괴되면 이 공격은 못 씀</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>windup: 전조 시간(초). 이 시간이 끝나는 순간이 회피 타이밍. weight: 공격 선택 가중치</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Config combat_*: 회피 판정 시간, 플레이어 피해, 방어 배율, 도주 확률, 기만 전환 시점</t>
         </is>
       </c>
     </row>
@@ -1067,14 +1732,11 @@
           <t>ep_test1</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>노드 E (주사위 판정 테스트)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1087,7 +1749,6 @@
           <t>ep_test1</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>판정 성공 노드</t>
@@ -1098,7 +1759,6 @@
           <t>t1_e</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1111,7 +1771,6 @@
           <t>ep_test1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>판정 실패 노드</t>
@@ -1122,7 +1781,6 @@
           <t>t1_e</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1766,10 +2424,6 @@
           <t>판정 테스트로</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>t1_e</t>
@@ -1792,9 +2446,6 @@
           <t>판정 A (능력치 A, 목표 12)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>setflag:dice_ok</t>
@@ -1845,10 +2496,6 @@
           <t>판정 B (능력치 B, 목표 10, 상황 보정 -5)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>t1_dice_ok</t>
@@ -1892,9 +2539,6 @@
           <t>능력치 A 성장 (+1)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>abil:stat_a+1</t>
@@ -1932,8 +2576,6 @@
           <t>gray</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>t1_e</t>
@@ -1956,10 +2598,6 @@
           <t>노드 D로</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>t1_d</t>
@@ -2623,7 +3261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2753,6 +3391,96 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>combat_perfect_window</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>완벽 회피 허용 오차 (초, ±)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>combat_normal_window</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>일반 회피 허용 오차 (초, ±)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>combat_player_damage</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>플레이어 공격 피해</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>combat_defend_mult</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>방어 시 받는 피해 배율</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>combat_flee_chance</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>50</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>도주 성공 확률 (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>combat_feint_switch</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>기만 공격 전조가 바뀌는 시점 (전조 시간 비율)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -20,7 +20,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyParts" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyAttacks" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldObjects" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,7 +687,6 @@
       <c r="D4" t="n">
         <v>25</v>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -707,7 +707,6 @@
       <c r="D5" t="n">
         <v>25</v>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -728,7 +727,6 @@
       <c r="D6" t="n">
         <v>25</v>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -749,7 +747,6 @@
       <c r="D7" t="n">
         <v>25</v>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -925,7 +922,6 @@
       <c r="E4" t="n">
         <v>70</v>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -949,7 +945,6 @@
       <c r="E5" t="n">
         <v>70</v>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1198,7 +1193,259 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>object_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>map_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>marker</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>patrol</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>fo_enemy1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>test_field</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>enemy_test</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>적 A (테스트)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>right 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fo_enemy2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>test_field</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>enemy_test</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>적 A (테스트)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>down 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fo_look1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>test_field</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>investigate</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>spot_b</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>조사 지점 1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>조사 텍스트 1 (테스트)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fo_look2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test_field</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>investigate</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>조사 지점 2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>조사 텍스트 2 (테스트, 아이템 없음)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>fo_look3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test_field</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>investigate</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>spot_empty</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>조사 지점 3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>조사 텍스트 3 (테스트, 빈 탐색)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1584,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -1387,9 +1633,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -1429,6 +1673,30 @@
       <c r="A37" t="inlineStr">
         <is>
           <t>Config combat_*: 회피 판정 시간, 플레이어 피해, 방어 배율, 도주 확률, 기만 전환 시점</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>[탐험] 맵 모양: tools/maps/&lt;map_id&gt;.txt  (# 벽, . 바닥, P 시작 위치, 그 밖의 글자 = FieldObjects 의 marker)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FieldObjects: type enemy(ref=enemy_id, patrol='right 4' 처럼 방향+칸수 왕복) / investigate(text 표시, ref=Loot spot_id 면 아이템 굴림)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Config field_*: 칸 크기, 이동·순찰·추격 속도, 시야, 추격 포기 거리, 도주 후 유예 시간</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3481,6 +3749,111 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>field_tile</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>48</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>탐험 맵 한 칸 크기 (픽셀)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>field_player_speed</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>플레이어 이동 속도 (칸/초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>field_enemy_speed</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>적 순찰 속도 (칸/초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>field_enemy_chase_speed</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>적 추격 속도 (칸/초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>field_enemy_sight</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>적 시야 (칸). 벽 너머는 못 봄</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>field_enemy_lose_sight</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>이 거리 넘게 멀어지면 추격 포기 (칸)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>field_flee_grace</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>도주 후 적이 다시 덤비지 않는 시간 (초)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -1193,7 +1193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1279,7 +1279,6 @@
           <t>적 A (테스트)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>right 5</t>
@@ -1317,7 +1316,6 @@
           <t>적 A (테스트)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>down 3</t>
@@ -1360,7 +1358,6 @@
           <t>조사 텍스트 1 (테스트)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1383,7 +1380,6 @@
           <t>investigate</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>조사 지점 2</t>
@@ -1394,7 +1390,6 @@
           <t>조사 텍스트 2 (테스트, 아이템 없음)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1432,7 +1427,74 @@
           <t>조사 텍스트 3 (테스트, 빈 탐색)</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>fo_npc1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>test_field</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>fd_npc1_a</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NPC 1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>fo_npc2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>test_field</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>fd_npc2_a</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NPC 2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1445,7 +1507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1633,7 +1695,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -1676,9 +1737,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
@@ -1697,6 +1756,30 @@
       <c r="A41" t="inlineStr">
         <is>
           <t>Config field_*: 칸 크기, 이동·순찰·추격 속도, 시야, 추격 포기 거리, 도주 후 유예 시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>[필드 대화] Nodes 에서 episode_id 를 비운 노드 = 필드 대화. 대화를 끝낼 때 next_node(또는 fail_next)에 EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FieldObjects type=npc, ref=필드 대화 시작 노드. 말을 걸 때마다 시작 노드부터 (조건·플래그로 내용 분기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Config protagonist_id: 탐험 중 주인공 (능력치·능력·주사위 보정)</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2133,118 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fd_npc1_a</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>char_npc</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>필드 대화 노드 1 (NPC 1)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fd_npc1_b</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>char_t1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>필드 대화 노드 2 (주인공)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fd_npc1_fail</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>char_npc</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>필드 대화 노드 3 (판정 실패)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fd_npc2_a</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>char_npc2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>필드 대화 노드 4 (NPC 2)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>fd_npc2_b</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>char_npc2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>필드 대화 노드 5 (flag:showed_knife 일 때만)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2061,7 +2256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.4" customWidth="1" min="1" max="1"/>
@@ -2869,6 +3064,209 @@
       <c r="H24" t="inlineStr">
         <is>
           <t>t1_d</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>fdc1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>fd_npc1_a</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>대화 선택지 1 (일반)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>fd_npc1_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>fdc2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>fd_npc1_a</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>칼 보여주기</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>has:knife</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>gray</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>setflag:showed_knife</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>fd_npc1_b</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fdc3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fd_npc1_a</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>설득 (능력치 A, 목표 12)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>item:+bandage</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>fd_npc1_b</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>dice</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stat_a</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>12</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>fd_npc1_fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>fdc4</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fd_npc1_a</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>대화 끝내기</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>fdc5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fd_npc2_a</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>칼 이야기 (flag:showed_knife)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>flag:showed_knife</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>fd_npc2_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>fdc6</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>fd_npc2_a</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>대화 끝내기</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>EXIT</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3854,6 +4252,23 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>protagonist_id</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>char_t1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>주인공 char_id (탐험·필드 대화의 능력치·능력·대화 배치)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -21,7 +21,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyParts" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyAttacks" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldObjects" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Survival" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CampActions" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1193,7 +1195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1459,8 +1461,6 @@
           <t>NPC 1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1493,8 +1493,142 @@
           <t>NPC 2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>fo_camp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>basecamp</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>camp</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>베이스캠프 거점</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>fo_to_field</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>basecamp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>test_field</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>탐험 지역으로</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>fo_to_camp</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>test_field</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>basecamp</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>베이스캠프로</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fo_supply</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>test_field</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>investigate</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>spot_supply</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>보급 상자</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>조사 텍스트 4 (테스트, 음식·물)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1507,7 +1641,375 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>param_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>decay_per_hour</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>warn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hunger</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>포만감</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>thirst</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>수분</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sleep</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>수면</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hygiene</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>위생</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mental</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>멘탈</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>action_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>effects</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>camp_eat</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>식사 (통조림 1개)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>has:food</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>item:-food;surv:hunger+50</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>camp_drink</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>물 마시기 (물 1병)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>has:water</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>item:-water;surv:thirst+60</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>camp_sleep4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>수면 (4시간)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>240</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>surv:sleep+40</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>camp_sleep8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>수면 (8시간)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>480</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>surv:sleep+80;surv:mental+10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>camp_wash</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>씻기</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>surv:hygiene+60</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>camp_save</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>save</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1737,7 +2239,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
@@ -1759,9 +2260,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -1780,6 +2279,44 @@
       <c r="A45" t="inlineStr">
         <is>
           <t>Config protagonist_id: 탐험 중 주인공 (능력치·능력·주사위 보정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>[생존] Survival: 파라미터 (100 = 좋음, 0 = 최악). decay_per_hour = 게임 1시간마다 줄어드는 양, warn = 경고 표시 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>조건 surv:hunger&lt;30 / 효과 surv:hunger+40</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>[베이스캠프] CampActions: 베이스캠프 거점(FieldObjects type=camp)에서 고르는 행동. minutes = 걸리는 시간, kind=save 는 저장</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>FieldObjects type=exit: ref = 이동할 맵 이름. 도착하면 그 맵의 P 위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Config start_map / basecamp_map / time_scale(실제 1초 = 게임 몇 분) / start_hour</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2676,6 @@
           <t>fd_npc1_a</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>char_npc</t>
@@ -2150,8 +2686,6 @@
           <t>필드 대화 노드 1 (NPC 1)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2159,7 +2693,6 @@
           <t>fd_npc1_b</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>char_t1</t>
@@ -2175,7 +2708,6 @@
           <t>EXIT</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2183,7 +2715,6 @@
           <t>fd_npc1_fail</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>char_npc</t>
@@ -2199,7 +2730,6 @@
           <t>EXIT</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2207,7 +2737,6 @@
           <t>fd_npc2_a</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>char_npc2</t>
@@ -2218,8 +2747,6 @@
           <t>필드 대화 노드 4 (NPC 2)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2227,7 +2754,6 @@
           <t>fd_npc2_b</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>char_npc2</t>
@@ -2243,7 +2769,6 @@
           <t>EXIT</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3083,10 +3608,6 @@
           <t>대화 선택지 1 (일반)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>fd_npc1_b</t>
@@ -3119,7 +3640,6 @@
           <t>gray</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>setflag:showed_knife</t>
@@ -3152,9 +3672,6 @@
           <t>설득 (능력치 A, 목표 12)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>item:+bandage</t>
@@ -3200,10 +3717,6 @@
           <t>대화 끝내기</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>EXIT</t>
@@ -3236,8 +3749,6 @@
           <t>hide</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>fd_npc2_b</t>
@@ -3260,10 +3771,6 @@
           <t>대화 끝내기</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>EXIT</t>
@@ -3281,7 +3788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.2" customWidth="1" min="1" max="1"/>
@@ -3445,6 +3952,66 @@
         <v>3</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>통조림(테스트)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>아이템 설명 5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>item:-food;surv:hunger+40</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>물(테스트)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>아이템 설명 6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>item:-water;surv:thirst+50</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3456,7 +4023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.2" customWidth="1" min="1" max="1"/>
@@ -3575,6 +4142,58 @@
       </c>
       <c r="F4" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>l4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>spot_supply</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>l5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>spot_supply</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3927,7 +4546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4269,6 +4888,70 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>start_map</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>basecamp</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>새 회차를 시작하는 맵</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>basecamp_map</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>basecamp</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>베이스캠프 맵 (저장 가능한 유일한 곳)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>time_scale</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>탐험 중 실제 1초에 흐르는 게임 시간 (분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>start_hour</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>새 회차 시작 시각 (시)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -1515,14 +1515,11 @@
           <t>camp</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>베이스캠프 거점</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1555,8 +1552,6 @@
           <t>탐험 지역으로</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1589,8 +1584,6 @@
           <t>베이스캠프로</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1628,7 +1621,6 @@
           <t>조사 텍스트 4 (테스트, 음식·물)</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1882,7 +1874,6 @@
           <t>item:-food;surv:hunger+50</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1908,7 +1899,6 @@
           <t>item:-water;surv:thirst+60</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1918,19 +1908,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>수면 (4시간)</t>
+          <t>짧게 자기</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>240</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>surv:sleep+40</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1940,19 +1928,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>수면 (8시간)</t>
+          <t>푹 자기</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>480</v>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>surv:sleep+80;surv:mental+10</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1968,13 +1954,11 @@
       <c r="C6" t="n">
         <v>30</v>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>surv:hygiene+60</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1990,8 +1974,6 @@
       <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>save</t>
@@ -2260,7 +2242,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -2282,9 +2263,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -1195,7 +1195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1206,6 +1206,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1249,6 +1250,11 @@
           <t>patrol</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1619,6 +1625,45 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>조사 텍스트 4 (테스트, 음식·물)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fo_cat</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>basecamp</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>npc</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>fd_cat_a</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>고양이</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>!wflag:cat_away</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1903,80 +1948,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>camp_sleep4</t>
+          <t>camp_wash</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>짧게 자기</t>
+          <t>씻기</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>surv:sleep+40</t>
+          <t>surv:hygiene+60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>camp_sleep8</t>
+          <t>camp_sleep</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>푹 자기</t>
+          <t>잠자기</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>480</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>surv:sleep+80;surv:mental+10</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>camp_wash</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>씻기</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>surv:hygiene+60</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>camp_save</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>저장</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>save</t>
+          <t>surv:sleep+10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sleep</t>
         </is>
       </c>
     </row>
@@ -1991,7 +2002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A51"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -2263,7 +2274,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -2296,6 +2306,37 @@
       <c r="A51" t="inlineStr">
         <is>
           <t>Config start_map / basecamp_map / time_scale(실제 1초 = 게임 몇 분) / start_hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>[저장] 베이스캠프에서만. 고양이(FieldObjects condition 이 참일 때만 나타남)에게 효과 save 로 저장하거나, 잠자기(CampActions kind=sleep)로 자고 나면 저장</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>효과 save: 회차 저장 (베이스캠프 밖에서는 '여기서는 저장할 수 없다')</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CampActions kind=sleep: minutes=60, effects 는 1시간마다 적용, 1~sleep_max_hours 시간 중 골라 잔다</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>FieldObjects.condition: 맵에 들어올 때 참이어야 물체가 나타남 (비우면 항상)</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2749,6 +2790,26 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>fd_cat_a</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>char_cat</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>고양이 노드 (테스트, 사람 말을 하지 않는다)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2760,7 +2821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.4" customWidth="1" min="1" max="1"/>
@@ -3751,6 +3812,62 @@
         </is>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fdc_cat1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>fd_cat_a</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>쓰다듬는다 (저장)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>save</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>fdc_cat2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fd_cat_a</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>그냥 둔다</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
@@ -4186,7 +4303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.8" customWidth="1" min="1" max="1"/>
@@ -4300,6 +4417,25 @@
           <t>#4FC3F7</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>char_cat</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>고양이</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>#E8B04A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4525,7 +4661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4931,6 +5067,21 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sleep_max_hours</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>12</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한 번에 잘 수 있는 최대 시간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -1195,7 +1195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1207,6 +1207,7 @@
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1255,6 +1256,11 @@
           <t>condition</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1659,11 +1665,9 @@
           <t>고양이</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>!wflag:cat_away</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>06:00-12:00, 20:00-23:00</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1983,6 @@
       <c r="C5" t="n">
         <v>60</v>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>surv:sleep+10</t>
@@ -2002,7 +2005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A56"/>
+  <dimension ref="A1:A57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -2309,9 +2312,6 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-    </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
@@ -2337,6 +2337,13 @@
       <c r="A56" t="inlineStr">
         <is>
           <t>FieldObjects.condition: 맵에 들어올 때 참이어야 물체가 나타남 (비우면 항상)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FieldObjects.schedule (npc): 하루 중 있는 시간대 '06:00-12:00, 20:00-23:00'. 자정 넘김 '22:00-02:00' 가능. 시간이 흐르면 나타나고 사라짐</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2803,6 @@
           <t>fd_cat_a</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>char_cat</t>
@@ -2807,8 +2813,6 @@
           <t>고양이 노드 (테스트, 사람 말을 하지 않는다)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3833,9 +3837,6 @@
           <t>쓰다듬는다 (저장)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>save</t>
@@ -3863,10 +3864,6 @@
           <t>그냥 둔다</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>EXIT</t>
@@ -4429,13 +4426,11 @@
           <t>고양이</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>#E8B04A</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -4883,11 +4883,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>탐험 맵 한 칸 크기 (픽셀)</t>
+          <t>탐험 맵 한 칸 크기 (픽셀, 1920x1080 기준)</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -4656,7 +4656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5077,6 +5077,21 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sleep_default_hours</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>잠자기를 고를 때 처음 표시되는 시간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -1957,15 +1957,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>씻기</t>
+          <t>씻기 (물 1병)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>30</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>has:water</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>surv:hygiene+60</t>
+          <t>item:-water;surv:hygiene+60</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -23,7 +23,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldObjects" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Survival" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CampActions" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revivals" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1394,6 +1395,11 @@
           <t>investigate</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>spot_charm</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>조사 지점 2</t>
@@ -1401,7 +1407,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>조사 텍스트 2 (테스트, 아이템 없음)</t>
+          <t>조사 텍스트 2 (테스트, 부활 아이템)</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2016,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A57"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>revive_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>effects</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rv_charm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>부활 부적</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>has:charm</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>item:-charm</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>부활 텍스트 1 (테스트, 아이템으로 부활)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rv_hana</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>초월체의 보호</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flag:hana_protect</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>clearflag:hana_protect</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>부활 텍스트 2 (테스트, 초월체가 부활시킴)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -2349,6 +2457,30 @@
       <c r="A57" t="inlineStr">
         <is>
           <t>FieldObjects.schedule (npc): 하루 중 있는 시간대 '06:00-12:00, 20:00-23:00'. 자정 넘김 '22:00-02:00' 가능. 시간이 흐르면 나타나고 사라짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>[부활] Revivals: 사망 순간 위에서부터 condition 이 참인 첫 행으로 부활. effects 적용(예: 아이템 소모), text 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → 소지품·시간·생존·부상·플래그 모두 유지한 채 베이스캠프(P)에서 깨어남. 맞는 행이 없으면 게임 처음부터</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>맵 글자 S: 새 회차 시작 위치 (Config start_map 의 맵). 없으면 P</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.4" customWidth="1" min="1" max="1"/>
@@ -3875,6 +4007,44 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fdc_cat3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fd_cat_a</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>(테스트) 부활 보호 받기</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>!flag:hana_protect</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>setflag:hana_protect</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3886,7 +4056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.2" customWidth="1" min="1" max="1"/>
@@ -4110,6 +4280,32 @@
         <v>5</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>charm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>부활 부적(테스트)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>relic</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>아이템 설명 7</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4121,7 +4317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.2" customWidth="1" min="1" max="1"/>
@@ -4292,6 +4488,32 @@
       </c>
       <c r="F6" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>l6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>spot_charm</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>charm</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5011,12 +5233,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>basecamp</t>
+          <t>test_field</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>새 회차를 시작하는 맵</t>
+          <t>새 회차(첫 시작·부활 없는 사망 후)를 시작하는 맵. 그 맵의 S 위치에서 깨어남</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -2460,9 +2460,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-    </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
@@ -2481,6 +2479,13 @@
       <c r="A61" t="inlineStr">
         <is>
           <t>맵 글자 S: 새 회차 시작 위치 (Config start_map 의 맵). 없으면 P</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Config save_slots: 저장 슬롯 수. 잠에서 깨거나 효과 save(고양이)로 저장할 때 슬롯을 고름</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4038,6 @@
           <t>hide</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>setflag:hana_protect</t>
@@ -4301,7 +4305,6 @@
           <t>아이템 설명 7</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>1</v>
       </c>
@@ -4883,7 +4886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5319,6 +5322,21 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>save_slots</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>저장 슬롯 수 (저장·이어하기 때 고른다)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -2460,7 +2460,6 @@
         </is>
       </c>
     </row>
-    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
@@ -2500,7 +2499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2839,123 +2838,6 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>fd_npc1_a</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>char_npc</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>필드 대화 노드 1 (NPC 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>fd_npc1_b</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>char_t1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>필드 대화 노드 2 (주인공)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>fd_npc1_fail</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>char_npc</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>필드 대화 노드 3 (판정 실패)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>fd_npc2_a</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>char_npc2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>필드 대화 노드 4 (NPC 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>fd_npc2_b</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>char_npc2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>필드 대화 노드 5 (flag:showed_knife 일 때만)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>fd_cat_a</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>char_cat</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>고양이 노드 (테스트, 사람 말을 하지 않는다)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2967,7 +2849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.4" customWidth="1" min="1" max="1"/>
@@ -3775,277 +3657,6 @@
       <c r="H24" t="inlineStr">
         <is>
           <t>t1_d</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>fdc1</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>fd_npc1_a</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>대화 선택지 1 (일반)</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>fd_npc1_b</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>fdc2</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>fd_npc1_a</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>칼 보여주기</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>has:knife</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>gray</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>setflag:showed_knife</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>fd_npc1_b</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>fdc3</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>fd_npc1_a</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>설득 (능력치 A, 목표 12)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>item:+bandage</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>fd_npc1_b</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>dice</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stat_a</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>12</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>fd_npc1_fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>fdc4</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>fd_npc1_a</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>대화 끝내기</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>fdc5</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>fd_npc2_a</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>칼 이야기 (flag:showed_knife)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>flag:showed_knife</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>fd_npc2_b</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>fdc6</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>fd_npc2_a</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>대화 끝내기</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>fdc_cat1</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>fd_cat_a</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>쓰다듬는다 (저장)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>save</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>fdc_cat2</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>fd_cat_a</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>그냥 둔다</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>fdc_cat3</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>fd_cat_a</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>(테스트) 부활 보호 받기</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>!flag:hana_protect</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>setflag:hana_protect</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>EXIT</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -20,11 +20,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyParts" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyAttacks" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldObjects" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Survival" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CampActions" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revivals" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Survival" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CampActions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revivals" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1196,498 +1195,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>object_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>map_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>marker</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ref</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>patrol</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>schedule</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>fo_enemy1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>test_field</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>enemy_test</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>적 A (테스트)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>right 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>fo_enemy2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>test_field</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>enemy_test</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>적 A (테스트)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>down 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>fo_look1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>test_field</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>investigate</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>spot_b</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>조사 지점 1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>조사 텍스트 1 (테스트)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>fo_look2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>test_field</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>investigate</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>spot_charm</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>조사 지점 2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>조사 텍스트 2 (테스트, 부활 아이템)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>fo_look3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>test_field</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>investigate</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>spot_empty</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>조사 지점 3</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>조사 텍스트 3 (테스트, 빈 탐색)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>fo_npc1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>test_field</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>fd_npc1_a</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NPC 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>fo_npc2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>test_field</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>fd_npc2_a</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>NPC 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>fo_camp</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>basecamp</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>camp</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>베이스캠프 거점</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>fo_to_field</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>basecamp</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>exit</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>test_field</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>탐험 지역으로</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>fo_to_camp</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>test_field</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>exit</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>basecamp</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>베이스캠프로</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>fo_supply</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>test_field</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>investigate</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>spot_supply</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>보급 상자</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>조사 텍스트 4 (테스트, 음식·물)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>fo_cat</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>basecamp</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>npc</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>fd_cat_a</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>고양이</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>06:00-12:00, 20:00-23:00</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1856,7 +1363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2010,7 +1517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2112,13 +1619,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A62"/>
+  <dimension ref="A1:A63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -2131,6 +1638,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2166,6 +1674,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -2208,6 +1717,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -2257,6 +1767,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -2306,6 +1817,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -2348,20 +1860,9 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>[탐험] 맵 모양: tools/maps/&lt;map_id&gt;.txt  (# 벽, . 바닥, P 시작 위치, 그 밖의 글자 = FieldObjects 의 marker)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>FieldObjects: type enemy(ref=enemy_id, patrol='right 4' 처럼 방향+칸수 왕복) / investigate(text 표시, ref=Loot spot_id 면 아이템 굴림)</t>
-        </is>
-      </c>
-    </row>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -2369,6 +1870,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -2376,13 +1878,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>FieldObjects type=npc, ref=필드 대화 시작 노드. 말을 걸 때마다 시작 노드부터 (조건·플래그로 내용 분기)</t>
-        </is>
-      </c>
-    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -2390,6 +1886,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -2404,20 +1901,8 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>[베이스캠프] CampActions: 베이스캠프 거점(FieldObjects type=camp)에서 고르는 행동. minutes = 걸리는 시간, kind=save 는 저장</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>FieldObjects type=exit: ref = 이동할 맵 이름. 도착하면 그 맵의 P 위치</t>
-        </is>
-      </c>
-    </row>
+    <row r="49"/>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
@@ -2425,13 +1910,8 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>[저장] 베이스캠프에서만. 고양이(FieldObjects condition 이 참일 때만 나타남)에게 효과 save 로 저장하거나, 잠자기(CampActions kind=sleep)로 자고 나면 저장</t>
-        </is>
-      </c>
-    </row>
+    <row r="52"/>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -2446,20 +1926,9 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>FieldObjects.condition: 맵에 들어올 때 참이어야 물체가 나타남 (비우면 항상)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>FieldObjects.schedule (npc): 하루 중 있는 시간대 '06:00-12:00, 20:00-23:00'. 자정 넘김 '22:00-02:00' 가능. 시간이 흐르면 나타나고 사라짐</t>
-        </is>
-      </c>
-    </row>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
@@ -2474,17 +1943,18 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>맵 글자 S: 새 회차 시작 위치 (Config start_map 의 맵). 없으면 P</t>
-        </is>
-      </c>
-    </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
           <t>Config save_slots: 저장 슬롯 수. 잠에서 깨거나 효과 save(고양이)로 저장할 때 슬롯을 고름</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>[맵] 맵 모양과 맵 위 물체(적·조사·NPC·거점·출구)는 Godot '맵' 탭에서 편집 → tools/maps/&lt;맵ID&gt;.json</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -1625,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1638,7 +1638,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1674,7 +1673,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1717,7 +1715,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -1767,7 +1764,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -1817,7 +1813,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -1860,9 +1855,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -1870,7 +1862,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -1878,7 +1869,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -1886,7 +1876,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -1901,8 +1890,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
@@ -1910,8 +1897,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -1926,9 +1911,6 @@
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
@@ -1943,7 +1925,6 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
@@ -1955,6 +1936,27 @@
       <c r="A63" t="inlineStr">
         <is>
           <t>[맵] 맵 모양과 맵 위 물체(적·조사·NPC·거점·출구)는 Godot '맵' 탭에서 편집 → tools/maps/&lt;맵ID&gt;.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>[사지 복구 거래 §10] 조건 cut:left_arm (그 팔다리가 잘렸나) / cut:any (하나라도). 대상은 PlayerParts 의 vital 이 아닌 부위</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>효과 restore:left_arm / restore:all (잘린 팔다리를 최대 HP로 복구). 대가는 같은 effects 에 함께 적어 즉시 지불 (예: item:-relic;restore:left_arm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>조건 count:death&gt;=1 / count:run&gt;=2 (월드 기록: 사망 횟수(부활 포함)·회차 수). 초월체의 '또 왔네' 분기용</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -1625,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A67"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1957,6 +1957,13 @@
       <c r="A67" t="inlineStr">
         <is>
           <t>조건 count:death&gt;=1 / count:run&gt;=2 (월드 기록: 사망 횟수(부활 포함)·회차 수). 초월체의 '또 왔네' 분기용</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Choices.type=combat (필드 대화 전용): check=enemy_id. 이기면 effects·next_node, 도주하면 fail_effects·fail_next, 지면 대화가 끝나고 사망 처리(Revivals)</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -779,6 +779,16 @@
           <t>name</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>flee_chance</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -790,6 +800,9 @@
         <is>
           <t>적 A (테스트)</t>
         </is>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A68"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1964,6 +1977,13 @@
       <c r="A68" t="inlineStr">
         <is>
           <t>Choices.type=combat (필드 대화 전용): check=enemy_id. 이기면 effects·next_node, 도주하면 fail_effects·fail_next, 지면 대화가 끝나고 사망 처리(Revivals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Enemies.flee_chance: 도주 성공률 % (주사위 1~100 이 이 값 이하면 성공, 비우면 Config combat_flee_chance). Enemies.image: 전투 화면 그림 res:// 경로 (비우면 도형)</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4427,6 +4447,21 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>combat_item_uses_turn</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>전투 중 아이템 사용이 턴을 쓰는지 (1 = 씀, 0 = 안 씀). TODO 기획 7.1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="10" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Episodes" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,33 +11,47 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choices" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loot" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Characters" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endings" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abilities" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlayerParts" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyParts" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyAttacks" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Npcs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endings" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abilities" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlayerParts" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NpcParts" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NpcAttacks" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Survival" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CampActions" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revivals" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -54,7 +67,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDE7F3"/>
+        <fgColor rgb="FFDDE7F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,12 +83,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -439,16 +453,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="24.4" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="2"/>
+    <col width="24.375" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="21.2" customWidth="1" min="6" max="6"/>
-    <col width="21.2" customWidth="1" min="7" max="7"/>
-    <col width="24.4" customWidth="1" min="8" max="8"/>
+    <col width="21.25" customWidth="1" min="6" max="7"/>
+    <col width="24.375" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -583,171 +595,425 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="19.625" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>part_id</t>
+          <t>key</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>hp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>vital</t>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>head</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>머리</t>
-        </is>
+          <t>inventory_slots</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>인벤토리 칸 수</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>torso</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>몸통</t>
-        </is>
+          <t>hp_start</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>에피소드 시작 체력</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>left_arm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>왼팔</t>
-        </is>
+          <t>hp_max</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>25</v>
+          <t>체력 최대치</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>right_arm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>오른팔</t>
-        </is>
+          <t>sanity_start</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>25</v>
+          <t>에피소드 시작 정신력</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>left_leg</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>왼다리</t>
-        </is>
+          <t>sanity_max</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>25</v>
+          <t>정신력 최대치</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>right_leg</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>오른다리</t>
-        </is>
+          <t>time_start</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>120</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>25</v>
+          <t>에피소드 시작 시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>time_max</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>120</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>시간 최대치</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>combat_perfect_window</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>완벽 회피 허용 오차 (초, ±)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>combat_normal_window</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>일반 회피 허용 오차 (초, ±)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>combat_player_damage</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>플레이어 공격 피해</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>combat_defend_mult</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>방어 시 받는 피해 배율</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>combat_flee_chance</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>50</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>도주 성공 확률 (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>combat_feint_switch</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>기만 공격 전조가 바뀌는 시점 (전조 시간 비율)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>field_tile</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>80</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>탐험 맵 한 칸 크기 (픽셀, 1920x1080 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>field_enemy_sight</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>적 시야 (칸). 벽 너머는 못 봄</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>field_enemy_lose_sight</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>이 거리 넘게 멀어지면 추격 포기 (칸)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>field_flee_grace</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>도주 후 적이 다시 덤비지 않는 시간 (초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>protagonist_id</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>char_t1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>주인공 char_id (탐험·필드 대화의 능력치·능력·대화 배치)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>start_map</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>test_field</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>새 회차(첫 시작·부활 없는 사망 후)를 시작하는 맵. 그 맵의 S 위치에서 깨어남</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>basecamp_map</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>basecamp</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>베이스캠프 맵 (저장 가능한 유일한 곳)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>time_scale</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>탐험 중 실제 1초에 흐르는 게임 시간 (분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>start_hour</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>새 회차 시작 시각 (시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sleep_max_hours</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한 번에 잘 수 있는 최대 시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sleep_default_hours</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>잠자기를 고를 때 처음 표시되는 시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>save_slots</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>저장 슬롯 수 (저장·이어하기 때 고른다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>combat_item_uses_turn</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>전투 중 아이템 사용이 턴을 쓰는지 (1 = 씀, 0 = 안 씀). TODO 기획 7.1</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -761,48 +1027,195 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>enemy_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>part_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>flee_chance</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>image</t>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>vital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>enemy_test</t>
+          <t>head</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>적 A (테스트)</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+          <t>머리</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>torso</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>몸통</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>50</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>left_arm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>왼팔</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>right_arm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>오른팔</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>left_leg</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>왼다리</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>right_leg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>오른다리</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -816,44 +1229,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>enemy_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>npc_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>part_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>hp</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>hit_chance</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>vital</t>
         </is>
@@ -879,9 +1298,12 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
         <v>50</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -907,9 +1329,12 @@
         <v>30</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>90</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -935,6 +1360,9 @@
         <v>15</v>
       </c>
       <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
         <v>70</v>
       </c>
     </row>
@@ -958,6 +1386,9 @@
         <v>15</v>
       </c>
       <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
         <v>70</v>
       </c>
     </row>
@@ -975,59 +1406,59 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>attack_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>enemy_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>npc_id</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>part</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>pattern</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>targets</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>windup</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
@@ -1209,12 +1640,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="2"/>
+    <col width="7" customWidth="1" min="3" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1383,7 +1812,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -1537,7 +1966,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -1638,8 +2067,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A69"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:A72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
   </cols>
@@ -1773,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Characters.name_color: 대화 이름표 색 (#RRGGBB). 비우면 기본색.</t>
+          <t>Player·Npcs.name_color: 대화 이름표 색 (#RRGGBB). 비우면 기본색.</t>
         </is>
       </c>
     </row>
@@ -1787,7 +2216,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>보정치 = 능력치(Characters.abilities + abil: 효과로 성장) + 소지 아이템 dice_bonus + 선택지 mod</t>
+          <t>보정치 = 능력치(Player 의 능력치 열 + abil: 효과로 성장) + 소지 아이템 dice_bonus + 선택지 mod</t>
         </is>
       </c>
     </row>
@@ -1808,49 +2237,49 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Abilities 시트: ability_id, name.  Characters.abilities: 'stat_a=3, stat_b=1'</t>
+          <t>Abilities 시트: 능력치 6개 이름 (strength 근력, endurance 지구력, intelligence 지능, health 건강, mental 정신력, divinity 신성력). ability_id 는 그대로, name 만 바꿀 것</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Items.dice_bonus: 'stat_a+2' 또는 'all+1' (소지 중이면 적용, 개수와 무관하게 1번)</t>
+          <t>Items.dice_bonus: 'strength+2' 또는 'all+1' (소지 중이면 적용, 개수와 무관하게 1번)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>조건 abil:stat_a&gt;=3 / 효과 abil:stat_a+1 (육성)</t>
+          <t>조건 abil:strength&gt;=3 / 효과 abil:strength+1 (육성)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[전투] PlayerParts: 플레이어 부위 (key = 회피 키 W/A/S/D, vital=Y 면 파괴 시 사망)</t>
+          <t>[전투] PlayerParts: 플레이어 부위 (key = 회피 키 W/A/S/D, attack = 부위별 공격력, vital=Y 면 파괴 시 사망)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Enemies / EnemyParts(적별 부위, hit_chance %) / EnemyAttacks(적 공격)</t>
+          <t>Npcs 중 NpcParts(부위별 hp·attack·hit_chance %)·NpcAttacks(공격)가 있는 NPC 는 싸울 수 있다 (맵의 적, 대화 전투 선택지)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EnemyAttacks.pattern: normal / quick / combo(targets 'head, torso' 순서대로) / feint(targets '전조&gt;실제')</t>
+          <t>NpcAttacks.pattern: normal / quick / combo(targets 'head, torso' 순서대로) / feint(targets '전조&gt;실제')</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EnemyAttacks.part: 이 공격을 쓰는 적 부위. 그 부위가 파괴되면 이 공격은 못 씀</t>
+          <t>NpcAttacks.part: 이 공격을 쓰는 NPC 부위. 그 부위가 파괴되면 이 공격은 못 씀.  attack(부위별 공격력)은 아직 피해 공식에 안 쓰임 (TODO)</t>
         </is>
       </c>
     </row>
@@ -1871,7 +2300,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Config field_*: 칸 크기, 이동·순찰·추격 속도, 시야, 추격 포기 거리, 도주 후 유예 시간</t>
+          <t>Config field_*: 칸 크기, 시야, 추격 포기 거리, 도주 후 유예 시간. 이동 속도는 Player·Npcs 의 walk_speed·run_speed (칸/초)</t>
         </is>
       </c>
     </row>
@@ -1983,7 +2412,21 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Enemies.flee_chance: 도주 성공률 % (주사위 1~100 이 이 값 이하면 성공, 비우면 Config combat_flee_chance). Enemies.image: 전투 화면 그림 res:// 경로 (비우면 도형)</t>
+          <t>Npcs.flee_chance: 도주 성공률 % (주사위 1~100 이 이 값 이하면 성공, 비우면 Config combat_flee_chance). Npcs.image: 전투 화면 그림 res:// 경로 (비우면 도형)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>[등장인물] Player = 주인공 (에피소드 protagonist_id·Config protagonist_id). Npcs = 모든 NPC·적 (NPC 와도 싸울 수 있다). 두 시트의 ID 는 서로 달라야 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>능력치 열: walk_speed 걷기·run_speed 달리기 (필드 칸/초. 플레이어는 Shift 로 달림, 적은 순찰=걷기·추격=달리기), strength 근력, endurance 지구력, intelligence 지능, health 건강, mental 정신력, divinity 신성력 (스킬용, TODO)</t>
         </is>
       </c>
     </row>
@@ -1999,14 +2442,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="37.2" customWidth="1" min="4" max="4"/>
-    <col width="30.8" customWidth="1" min="5" max="5"/>
-    <col width="53.2" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="3"/>
+    <col width="37.25" customWidth="1" min="4" max="4"/>
+    <col width="30.75" customWidth="1" min="5" max="5"/>
+    <col width="53.25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2349,22 +2790,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="16.4" customWidth="1" min="1" max="1"/>
-    <col width="13.2" customWidth="1" min="2" max="2"/>
+    <col width="16.375" customWidth="1" min="1" max="1"/>
+    <col width="13.25" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="37.2" customWidth="1" min="4" max="4"/>
-    <col width="16.4" customWidth="1" min="5" max="5"/>
-    <col width="24.4" customWidth="1" min="6" max="6"/>
-    <col width="38.8" customWidth="1" min="7" max="7"/>
-    <col width="27.6" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="37.25" customWidth="1" min="4" max="4"/>
+    <col width="16.375" customWidth="1" min="5" max="5"/>
+    <col width="24.375" customWidth="1" min="6" max="6"/>
+    <col width="38.75" customWidth="1" min="7" max="7"/>
+    <col width="27.625" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3018,7 +3454,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>stat_a</t>
+          <t>strength</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -3063,7 +3499,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stat_b</t>
+          <t>intelligence</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -3096,7 +3532,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>abil:stat_a+1</t>
+          <t>abil:strength+1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3118,12 +3554,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>능력치 조건 (abil:stat_a&gt;=4)</t>
+          <t>능력치 조건 (abil:strength&gt;=4)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>abil:stat_a&gt;=4</t>
+          <t>abil:strength&gt;=4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3171,14 +3607,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="13.2" customWidth="1" min="1" max="1"/>
-    <col width="16.4" customWidth="1" min="2" max="2"/>
+    <col width="13.25" customWidth="1" min="1" max="1"/>
+    <col width="16.375" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19.6" customWidth="1" min="4" max="4"/>
+    <col width="19.625" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="16.4" customWidth="1" min="6" max="6"/>
+    <col width="16.375" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3275,7 +3711,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stat_a+1</t>
+          <t>strength+1</t>
         </is>
       </c>
     </row>
@@ -3431,14 +3867,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="13.2" customWidth="1" min="1" max="1"/>
+    <col width="13.25" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="11.6" customWidth="1" min="4" max="4"/>
-    <col width="11.6" customWidth="1" min="5" max="5"/>
-    <col width="16.4" customWidth="1" min="6" max="6"/>
+    <col width="13.25" customWidth="1" min="3" max="3"/>
+    <col width="11.625" customWidth="1" min="4" max="5"/>
+    <col width="16.375" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3640,40 +4075,82 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14.8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="11.6" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>char_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>name_color</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>traits</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>name_color</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>abilities</t>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>walk_speed</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>run_speed</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>endurance</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>intelligence</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>mental</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>divinity</t>
         </is>
       </c>
     </row>
@@ -3690,18 +4167,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>#D81B4A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>tester</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>#D81B4A</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>stat_a=3, stat_b=0</t>
-        </is>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3715,61 +4211,29 @@
           <t>주인공 2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>stat_a=1, stat_b=2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>char_npc</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NPC 1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>#F2C200</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>char_npc2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NPC 2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>#4FC3F7</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>char_cat</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>고양이</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>#E8B04A</t>
-        </is>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3783,152 +4247,239 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24.4" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ending_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>episode_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>world_flags_set</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>npc_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>name_color</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>traits</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>flee_chance</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>walk_speed</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>run_speed</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>endurance</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>intelligence</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>mental</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>divinity</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>end_t1_clear</t>
+          <t>char_npc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ep_test1</t>
+          <t>NPC 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ep_test1_clear</t>
-        </is>
+          <t>#F2C200</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>end_t1_good</t>
+          <t>char_npc2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ep_test1</t>
+          <t>NPC 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ep_test1_clear</t>
-        </is>
+          <t>#4FC3F7</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>end_t1_timeout</t>
+          <t>char_cat</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ep_test1</t>
-        </is>
+          <t>고양이</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>#E8B04A</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>end_t1_death</t>
+          <t>enemy_test</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ep_test1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>end_t1_madness</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ep_test1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>end_t2_clear</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ep_test2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ep_test2_clear</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>end_t2_timeout</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ep_test2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>end_t2_death</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ep_test2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>end_t2_madness</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ep_test2</t>
-        </is>
+          <t>적 A (테스트)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3942,46 +4493,151 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24.375" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ability_id</t>
+          <t>ending_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>episode_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>world_flags_set</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>stat_a</t>
+          <t>end_t1_clear</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>능력치 A</t>
+          <t>ep_test1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ep_test1_clear</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stat_b</t>
+          <t>end_t1_good</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>능력치 B</t>
+          <t>ep_test1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ep_test1_clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>end_t1_timeout</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ep_test1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>end_t1_death</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ep_test1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>end_t1_madness</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ep_test1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>end_t2_clear</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ep_test2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ep_test2_clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>end_t2_timeout</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ep_test2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>end_t2_death</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ep_test2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>end_t2_madness</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ep_test2</t>
         </is>
       </c>
     </row>
@@ -3996,469 +4652,94 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="19.6" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ability_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>inventory_slots</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>인벤토리 칸 수</t>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>근력</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hp_start</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>에피소드 시작 체력</t>
+          <t>endurance</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>지구력</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hp_max</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>체력 최대치</t>
+          <t>intelligence</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>지능</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sanity_start</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>100</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>에피소드 시작 정신력</t>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>건강</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sanity_max</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>100</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>정신력 최대치</t>
+          <t>mental</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>정신력</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time_start</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>120</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>에피소드 시작 시간</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>time_max</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>120</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>시간 최대치</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>combat_perfect_window</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>완벽 회피 허용 오차 (초, ±)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>combat_normal_window</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>일반 회피 허용 오차 (초, ±)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>combat_player_damage</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>플레이어 공격 피해</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>combat_defend_mult</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>방어 시 받는 피해 배율</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>combat_flee_chance</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>50</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>도주 성공 확률 (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>combat_feint_switch</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>기만 공격 전조가 바뀌는 시점 (전조 시간 비율)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>field_tile</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>80</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>탐험 맵 한 칸 크기 (픽셀, 1920x1080 기준)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>field_player_speed</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>플레이어 이동 속도 (칸/초)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>field_enemy_speed</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>적 순찰 속도 (칸/초)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>field_enemy_chase_speed</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>적 추격 속도 (칸/초)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>field_enemy_sight</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>5</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>적 시야 (칸). 벽 너머는 못 봄</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>field_enemy_lose_sight</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>8</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>이 거리 넘게 멀어지면 추격 포기 (칸)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>field_flee_grace</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>도주 후 적이 다시 덤비지 않는 시간 (초)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>protagonist_id</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>char_t1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>주인공 char_id (탐험·필드 대화의 능력치·능력·대화 배치)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>start_map</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>test_field</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>새 회차(첫 시작·부활 없는 사망 후)를 시작하는 맵. 그 맵의 S 위치에서 깨어남</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>basecamp_map</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>basecamp</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>베이스캠프 맵 (저장 가능한 유일한 곳)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time_scale</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>탐험 중 실제 1초에 흐르는 게임 시간 (분)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>start_hour</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>8</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>새 회차 시작 시각 (시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>sleep_max_hours</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>12</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>한 번에 잘 수 있는 최대 시간</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>sleep_default_hours</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>8</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>잠자기를 고를 때 처음 표시되는 시간</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>save_slots</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>5</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>저장 슬롯 수 (저장·이어하기 때 고른다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>combat_item_uses_turn</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>전투 중 아이템 사용이 턴을 쓰는지 (1 = 씀, 0 = 안 씀). TODO 기획 7.1</t>
+          <t>divinity</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>신성력</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Episodes" sheetId="1" state="visible" r:id="rId1"/>
@@ -608,7 +608,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -644,7 +643,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -687,7 +685,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -737,7 +734,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -787,7 +783,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -830,9 +825,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -840,7 +832,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -848,7 +839,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -856,7 +846,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
@@ -871,8 +860,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -880,8 +867,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
@@ -896,9 +881,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -913,7 +895,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -928,7 +909,6 @@
         </is>
       </c>
     </row>
-    <row r="65"/>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
@@ -964,7 +944,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
@@ -2416,7 +2395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2834,6 +2813,66 @@
       <c r="C27" t="inlineStr">
         <is>
           <t>전투 중 아이템 사용이 턴을 쓰는지 (1 = 씀, 0 = 안 씀). TODO 기획 7.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>carry_max_weight</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>30</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>들 수 있는 최대 무게. 이 이상이면 움직일 수 없음 (TODO 기획: 임시값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>carry_heavy_weight</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>20</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>이 무게 이상이면 이동 속도가 느려짐 (TODO 기획: 임시값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>carry_heavy_speed_mult</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>무거울 때 이동 속도 배율 (TODO 기획: 임시값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ability_chart_max</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>능력치 육각형 그래프의 바깥 끝 값 (표시용)</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -2427,11 +2427,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>인벤토리 칸 수</t>
+          <t>가방이 없을 때 소지품 칸 수 (손에 든 것은 안 셈)</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -11,11 +11,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choices" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abilities" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Survival" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CampActions" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revivals" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StatusEffects" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Survival" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CampActions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revivals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -588,7 +589,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A73"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>revive_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>effects</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rv_charm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>부활 부적</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>has:charm</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>item:-charm</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>부활 텍스트 1 (테스트, 아이템으로 부활)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rv_hana</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>초월체의 보호</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flag:hana_protect</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>clearflag:hana_protect</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>부활 텍스트 2 (테스트, 초월체가 부활시킴)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -955,6 +1058,13 @@
       <c r="A73" t="inlineStr">
         <is>
           <t>능력치 열: walk_speed 걷기·run_speed 달리기 (필드 칸/초. 플레이어는 Shift 로 달림, 적은 순찰=걷기·추격=달리기), strength 근력, endurance 지구력, intelligence 지능, health 건강, mental 정신력, divinity 신성력 (스킬용, TODO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>[상태이상] StatusEffects: status_id, name, description (장비창 능력치 탭에서 이름에 마우스를 올리면 설명). 효과 status:+bleeding 걸기 / status:-bleeding 풀기, 조건 status:bleeding. 실제 효과는 아직 없음 (TODO 기획)</t>
         </is>
       </c>
     </row>
@@ -2395,6 +2505,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>status_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bleeding</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>(테스트) 효과 설명 — 기획 TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>nausea</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>매스꺼움</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>(테스트) 효과 설명 — 기획 TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>panic</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>공황</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(테스트) 효과 설명 — 기획 TODO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
@@ -2881,7 +3078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3053,7 +3250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3205,106 +3402,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>revive_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>rv_charm</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>부활 부적</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>has:charm</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>item:-charm</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>부활 텍스트 1 (테스트, 아이템으로 부활)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>rv_hana</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>초월체의 보호</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flag:hana_protect</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>clearflag:hana_protect</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>부활 텍스트 2 (테스트, 초월체가 부활시킴)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A74"/>
+  <dimension ref="A1:A75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1065,6 +1065,13 @@
       <c r="A74" t="inlineStr">
         <is>
           <t>[상태이상] StatusEffects: status_id, name, description (장비창 능력치 탭에서 이름에 마우스를 올리면 설명). 효과 status:+bleeding 걸기 / status:-bleeding 풀기, 조건 status:bleeding. 실제 효과는 아직 없음 (TODO 기획)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>[맵 이동] 효과 move:map_id (그 맵의 P) / move:map_id@arrive_id (그 맵의 도착 지점). 필드 대화·아이템·거점 행동에서만, 대화 중이면 대화가 끝난 뒤 이동</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -2599,7 +2599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3077,6 +3077,68 @@
       <c r="C31" t="inlineStr">
         <is>
           <t>능력치 육각형 그래프의 바깥 끝 값 (표시용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>text_speed_default</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>대사 기본 출력 속도: instant / slow / normal / fast (대화 파일·페이지에서 바꿀 수 있음). TODO 기획 §10.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>text_speed_slow</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>느림: 초당 글자 수 (임시값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>text_speed_normal</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>35</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>보통: 초당 글자 수 (임시값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>text_speed_fast</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>70</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>빠름: 초당 글자 수 (임시값)</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -11,12 +11,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choices" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abilities" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StatusEffects" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Survival" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CampActions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revivals" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Survival" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CampActions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revivals" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -589,108 +588,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>revive_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>rv_charm</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>부활 부적</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>has:charm</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>item:-charm</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>부활 텍스트 1 (테스트, 아이템으로 부활)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>rv_hana</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>초월체의 보호</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flag:hana_protect</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>clearflag:hana_protect</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>부활 텍스트 2 (테스트, 초월체가 부활시킴)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:A75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
@@ -707,10 +604,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>엑셀 파일 나눔: player.xlsx (Player·PlayerParts) / npc.xlsx (Npcs·NpcParts·NpcAttacks) / item.xlsx (Items·Loot) / 나머지는 이 파일</t>
-        </is>
-      </c>
-    </row>
+          <t>엑셀 파일 나눔: player.xlsx (Player·PlayerParts·EquipSlots·Traits) / npc.xlsx (Npcs·NpcParts·NpcAttacks) / item.xlsx (Items·Loot) / status.xlsx (StatusEffects) / 나머지는 이 파일</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -746,6 +644,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -788,6 +687,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -837,6 +737,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -886,6 +787,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -928,6 +830,9 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -935,6 +840,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -942,6 +848,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -949,6 +856,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
@@ -963,6 +871,8 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -970,6 +880,8 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
@@ -984,6 +896,9 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -998,6 +913,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -1012,6 +928,7 @@
         </is>
       </c>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
@@ -1047,6 +964,7 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
@@ -2512,93 +2430,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>status_id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>bleeding</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>출혈</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>(테스트) 효과 설명 — 기획 TODO</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>nausea</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>매스꺼움</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>(테스트) 효과 설명 — 기획 TODO</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>panic</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>공황</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>(테스트) 효과 설명 — 기획 TODO</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
@@ -3147,7 +2978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3319,7 +3150,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3471,4 +3302,106 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>revive_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>effects</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rv_charm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>부활 부적</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>has:charm</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>item:-charm</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>부활 텍스트 1 (테스트, 아이템으로 부활)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rv_hana</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>초월체의 보호</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flag:hana_protect</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>clearflag:hana_protect</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>부활 텍스트 2 (테스트, 초월체가 부활시킴)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -608,7 +608,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -644,7 +643,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -687,7 +685,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -737,7 +734,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -787,7 +783,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -830,9 +825,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -840,7 +832,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -848,7 +839,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -856,7 +846,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
@@ -871,8 +860,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -880,8 +867,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
@@ -896,9 +881,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -913,7 +895,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -928,7 +909,6 @@
         </is>
       </c>
     </row>
-    <row r="65"/>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
@@ -964,7 +944,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
@@ -2430,7 +2409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2970,6 +2949,21 @@
       <c r="C35" t="inlineStr">
         <is>
           <t>빠름: 초당 글자 수 (임시값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>creation_start_points</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>캐릭터 생성 시작 포인트 (긍정 특성은 소비, 부정 특성은 획득). 기획 §2.2</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -2409,7 +2409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2964,6 +2964,21 @@
       <c r="C36" t="inlineStr">
         <is>
           <t>캐릭터 생성 시작 포인트 (긍정 특성은 소비, 부정 특성은 획득). 기획 §2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>combat_talk_uses_turn</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>전투 중 '대화'가 턴을 쓰나 (1 = 대화 뒤 적 차례, 0 = 다시 내 차례). TODO 기획</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -2409,7 +2409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2979,6 +2979,23 @@
       <c r="C37" t="inlineStr">
         <is>
           <t>전투 중 '대화'가 턴을 쓰나 (1 = 대화 뒤 적 차례, 0 = 다시 내 차례). TODO 기획</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>opening_dialogue</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>opening_in</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>새 게임(캐릭터 생성 직후) 오프닝 컷신의 첫 노드. 비우면 없음 (지금은 테스트용 opening.json)</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A75"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -969,6 +969,14 @@
       <c r="A75" t="inlineStr">
         <is>
           <t>[맵 이동] 효과 move:map_id (그 맵의 P) / move:map_id@arrive_id (그 맵의 도착 지점). 필드 대화·아이템·거점 행동에서만, 대화 중이면 대화가 끝난 뒤 이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>오프닝 컷신: 대화 에디터에서 대화 시작 카드 → '🎬 게임 오프닝으로 쓰기' 체크 (대화 하나만). 엑셀로 정하려면 Config 에 opening_dialogue = 첫 노드 ID 줄을 추가 (그쪽이 먼저)</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2979,23 +2987,6 @@
       <c r="C37" t="inlineStr">
         <is>
           <t>전투 중 '대화'가 턴을 쓰나 (1 = 대화 뒤 적 차례, 0 = 다시 내 차례). TODO 기획</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>opening_dialogue</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>opening_in</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>새 게임(캐릭터 생성 직후) 오프닝 컷신의 첫 노드. 비우면 없음 (지금은 테스트용 opening.json)</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -972,7 +972,6 @@
         </is>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -2417,7 +2416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2987,6 +2986,21 @@
       <c r="C37" t="inlineStr">
         <is>
           <t>전투 중 '대화'가 턴을 쓰나 (1 = 대화 뒤 적 차례, 0 = 다시 내 차례). TODO 기획</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>tile_art_px</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>16</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>픽셀아트 타일 한 칸의 그림 크기 (px). 게임에서는 field_tile(80) 로 늘려 그림 (5배)</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -15,7 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Survival" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CampActions" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revivals" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DeathCauses" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -588,6 +589,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>cause_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>starvation</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>굶주림</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>굶어 죽었습니다.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Survival hunger 가 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dehydration</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>탈수</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>탈수로 죽었습니다.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Survival thirst 가 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>{enemy}의 공격</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>전투에서 짐. text 를 비우면 '{name}(으)로 인해 사망했습니다.' ({enemy} = 상대 이름)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>알 수 없는 원인</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>원인을 모를 때</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
@@ -2416,7 +2539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3001,6 +3124,21 @@
       <c r="C38" t="inlineStr">
         <is>
           <t>픽셀아트 타일 한 칸의 그림 크기 (px). 게임에서는 field_tile(80) 로 늘려 그림 (5배)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>revive_survival_floor</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>10</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>부활할 때 생존 수치가 이보다 낮으면 이 값으로 (0 이면 바로 다시 죽으므로). 임시값 TODO 기획</t>
         </is>
       </c>
     </row>
@@ -3015,13 +3153,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="2"/>
     <col width="7" customWidth="1" min="3" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3055,6 +3194,11 @@
           <t>warn</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>death_cause</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3079,6 +3223,11 @@
       <c r="F2" t="n">
         <v>30</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>starvation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3102,6 +3251,11 @@
       </c>
       <c r="F3" t="n">
         <v>30</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>dehydration</t>
+        </is>
       </c>
     </row>
     <row r="4">

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -675,7 +675,6 @@
           <t>{enemy}의 공격</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>전투에서 짐. text 를 비우면 '{name}(으)로 인해 사망했습니다.' ({enemy} = 상대 이름)</t>
@@ -693,7 +692,6 @@
           <t>알 수 없는 원인</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>원인을 모를 때</t>
@@ -2539,7 +2537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3139,6 +3137,96 @@
       <c r="C39" t="inlineStr">
         <is>
           <t>부활할 때 생존 수치가 이보다 낮으면 이 값으로 (0 이면 바로 다시 죽으므로). 임시값 TODO 기획</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>noise_run_radius</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>몬스터 AI 청각: 달리면 이 반경(칸) 안의 BT 몬스터가 들음. 임시값 TODO 기획</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>noise_door_radius</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>몬스터 AI 청각: 문을 여닫으면 이 반경(칸). 임시값 TODO 기획</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>noise_interval</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>달리는 동안 소리를 내는 간격(초). 임시값</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ai_flashlight_sight_mult</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>손전등을 들고 있으면 몬스터 시야 × 이 값. 임시값 TODO 기획</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ai_follow_enabled</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1 = 쫓던 몬스터가 다른 맵까지 따라옴 (몬스터별로 맵 에디터 '따라오기' 끔 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ai_follow_delay</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>따라 들어오기까지 초. 임시값 TODO 기획</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -2537,7 +2537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3227,6 +3227,36 @@
       <c r="C45" t="inlineStr">
         <is>
           <t>따라 들어오기까지 초. 임시값 TODO 기획</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>combat_max_enemies</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한 번에 함께 싸우는 몬스터 최대 수 (NPC 는 늘 혼자)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>combat_join_radius</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>8</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>전투가 시작될 때 이 반경(칸) 안에서 쫓아오던 몬스터가 함께 들어옴. 임시값 TODO 기획</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -2537,7 +2537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3257,6 +3257,68 @@
       <c r="C47" t="inlineStr">
         <is>
           <t>전투가 시작될 때 이 반경(칸) 안에서 쫓아오던 몬스터가 함께 들어옴. 임시값 TODO 기획</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>player_sprite</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>res://art/characters/player.png</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>플레이어 캐릭터 그림 (프레임을 가로로 이어 붙인 PNG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>player_sprite_frames</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>그림 프레임 수 (걷는 동안 번갈아)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>player_sprite_frame_time</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>프레임 하나의 초 (달리면 0.6배)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>character_scale</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>캐릭터 그림 배율. 0 = 타일과 같은 픽셀 밀도 (field_tile / tile_art_px)</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -2537,7 +2537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3319,6 +3319,36 @@
       <c r="C51" t="inlineStr">
         <is>
           <t>캐릭터 그림 배율. 0 = 타일과 같은 픽셀 밀도 (field_tile / tile_art_px)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>window_light_energy</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>창문으로 들어오는 햇빛 밝기 (한낮 기준, 시간대에 따라 실외 sun_energy 비율로 줄어듦·밤엔 꺼짐) — 임시</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>window_light_radius</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>6</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>창문 빛이 닿는 거리 (칸) — 임시</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="13005" yWindow="1320" windowWidth="22635" windowHeight="18480" tabRatio="600" firstSheet="1" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Episodes" sheetId="1" state="visible" r:id="rId1"/>
@@ -49,7 +49,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -590,7 +594,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -2436,7 +2440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2537,7 +2541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2859,7 +2863,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>basecamp</t>
+          <t>new_america_in_church</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3349,6 +3353,53 @@
       <c r="C53" t="inlineStr">
         <is>
           <t>창문 빛이 닿는 거리 (칸) — 임시</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>vignette_strength</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>화면 가장자리 어둠 세기 (0 = 끔 ~ 1 = 가장자리 완전히 검게) — 임시</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>vignette_inner</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>어두워지기 시작하는 거리 (0 = 화면 가운데부터 ~ 1 = 가장자리 근처부터)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>vignette_color</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>#000000</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>비네트 색 (#RRGGBB)</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -2541,7 +2541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3400,6 +3400,51 @@
       <c r="C56" t="inlineStr">
         <is>
           <t>비네트 색 (#RRGGBB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>npc_wander_speed</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>돌아다니는 NPC 걷는 속도 (칸/초) — 임시</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>npc_wander_wait_min</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>돌아다니는 NPC 쉬는 시간 최소 (초) — 임시</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>npc_wander_wait_max</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>돌아다니는 NPC 쉬는 시간 최대 (초) — 임시</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -2541,7 +2541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3445,6 +3445,38 @@
       <c r="C59" t="inlineStr">
         <is>
           <t>돌아다니는 NPC 쉬는 시간 최대 (초) — 임시</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>view_mode</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>iso</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>게임 화면: iso = 쿼터뷰(아이소메트릭, 마름모) / topdown = 비스듬한 탑뷰 (규칙·맵은 같음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>iso_wall_height</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>120</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>쿼터뷰 벽 블록 높이 (화면 px, 한 칸 = 80) — 임시</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>iso</t>
+          <t>topdown</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/tools/sheets/content.xlsx
+++ b/tools/sheets/content.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="13005" yWindow="1320" windowWidth="22635" windowHeight="18480" tabRatio="600" firstSheet="1" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="13005" yWindow="1320" windowWidth="22635" windowHeight="18480" tabRatio="600" firstSheet="1" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Episodes" sheetId="1" state="visible" r:id="rId1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>char_t2</t>
+          <t>char_t1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -733,6 +733,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -768,6 +769,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -810,6 +812,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -859,6 +862,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -908,6 +912,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -950,6 +955,9 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -957,6 +965,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -964,6 +973,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -971,6 +981,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
@@ -985,6 +996,8 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -992,6 +1005,8 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
@@ -1006,6 +1021,9 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -1020,6 +1038,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -1034,6 +1053,7 @@
         </is>
       </c>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
@@ -1069,6 +1089,7 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
@@ -1097,6 +1118,7 @@
         </is>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -1306,7 +1328,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>char_t2</t>
+          <t>char_t1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2846,7 +2868,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>test_field</t>
+          <t>new_america_in_church</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
